--- a/SensitivityAnalysis/SingleSNP/MR_dat_binaryLR.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_dat_binaryLR.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="48">
   <si>
     <t>SNP</t>
   </si>
@@ -70,15 +70,39 @@
     <t>outcome</t>
   </si>
   <si>
-    <t>X</t>
+    <t>beta_95L</t>
+  </si>
+  <si>
+    <t>beta_95U</t>
+  </si>
+  <si>
+    <t>z</t>
   </si>
   <si>
     <t>pval.exposure</t>
   </si>
   <si>
+    <t>X_.log10_p.value</t>
+  </si>
+  <si>
+    <t>q_statistic</t>
+  </si>
+  <si>
+    <t>q_p.value</t>
+  </si>
+  <si>
+    <t>i2</t>
+  </si>
+  <si>
+    <t>n_studies</t>
+  </si>
+  <si>
     <t>N.exposure</t>
   </si>
   <si>
+    <t>effects</t>
+  </si>
+  <si>
     <t>se.exposure</t>
   </si>
   <si>
@@ -88,9 +112,6 @@
     <t>exposure</t>
   </si>
   <si>
-    <t>pos</t>
-  </si>
-  <si>
     <t>action</t>
   </si>
   <si>
@@ -116,6 +137,9 @@
   </si>
   <si>
     <t>Fracture</t>
+  </si>
+  <si>
+    <t>+++</t>
   </si>
   <si>
     <t>Sclerostin</t>
@@ -267,25 +291,46 @@
       <c r="AB1" t="s">
         <v>26</v>
       </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -300,16 +345,16 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="O2" t="n">
         <v>0.016678973778723176</v>
@@ -321,36 +366,57 @@
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0</v>
+        <v>0.028311</v>
       </c>
       <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -447,25 +513,46 @@
       <c r="AB1" t="s">
         <v>26</v>
       </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -480,16 +567,16 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="O2" t="n">
         <v>0.017419398346154382</v>
@@ -501,36 +588,57 @@
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0</v>
+        <v>0.028311</v>
       </c>
       <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -627,25 +735,46 @@
       <c r="AB1" t="s">
         <v>26</v>
       </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -660,16 +789,16 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O2" t="n">
         <v>0.02129732964239767</v>
@@ -681,36 +810,57 @@
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0</v>
+        <v>0.028311</v>
       </c>
       <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -807,25 +957,46 @@
       <c r="AB1" t="s">
         <v>26</v>
       </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -840,16 +1011,16 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
         <v>0.032857782726198936</v>
@@ -861,36 +1032,57 @@
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0</v>
+        <v>0.028311</v>
       </c>
       <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -987,25 +1179,46 @@
       <c r="AB1" t="s">
         <v>26</v>
       </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -1020,16 +1233,16 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O2" t="n">
         <v>0.009614765491649134</v>
@@ -1041,36 +1254,57 @@
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0</v>
+        <v>0.028311</v>
       </c>
       <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1167,25 +1401,46 @@
       <c r="AB1" t="s">
         <v>26</v>
       </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -1200,16 +1455,16 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>0.015820910871693763</v>
@@ -1221,36 +1476,57 @@
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0</v>
+        <v>0.028311</v>
       </c>
       <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>

--- a/SensitivityAnalysis/SingleSNP/MR_dat_binaryLR.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_dat_binaryLR.xlsx
@@ -333,16 +333,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08657116914557775</v>
+        <v>0.06583036304117222</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -357,13 +357,13 @@
         <v>39</v>
       </c>
       <c r="O2" t="n">
-        <v>0.016678973778723176</v>
+        <v>0.019283719131473427</v>
       </c>
       <c r="P2" t="n">
-        <v>2.098006599721131E-7</v>
+        <v>6.406842958793689E-4</v>
       </c>
       <c r="Q2" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R2" t="s">
         <v>39</v>
@@ -555,16 +555,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.018248869437388706</v>
+        <v>-0.021858841374728953</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -579,13 +579,13 @@
         <v>43</v>
       </c>
       <c r="O2" t="n">
-        <v>0.017419398346154382</v>
+        <v>0.02030462921415059</v>
       </c>
       <c r="P2" t="n">
-        <v>0.29481479490083357</v>
+        <v>0.2816837118964371</v>
       </c>
       <c r="Q2" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R2" t="s">
         <v>43</v>
@@ -777,16 +777,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.027049316458251003</v>
+        <v>-0.03880878470998141</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -801,13 +801,13 @@
         <v>44</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02129732964239767</v>
+        <v>0.02500193294663108</v>
       </c>
       <c r="P2" t="n">
-        <v>0.20405606765255724</v>
+        <v>0.12060687181714269</v>
       </c>
       <c r="Q2" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R2" t="s">
         <v>44</v>
@@ -999,16 +999,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0030275900167045025</v>
+        <v>0.018653373136791922</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1023,13 +1023,13 @@
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>0.032857782726198936</v>
+        <v>0.038745920128109276</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9265850208984425</v>
+        <v>0.6302122981891447</v>
       </c>
       <c r="Q2" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R2" t="s">
         <v>45</v>
@@ -1221,16 +1221,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0026409784804478855</v>
+        <v>-0.009631237479610276</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1245,13 +1245,13 @@
         <v>46</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009614765491649134</v>
+        <v>0.011170588184359365</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7835625219492152</v>
+        <v>0.3885796197774779</v>
       </c>
       <c r="Q2" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R2" t="s">
         <v>46</v>
@@ -1443,16 +1443,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04249482655464368</v>
+        <v>-0.0451874995156372</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1467,13 +1467,13 @@
         <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>0.015820910871693763</v>
+        <v>0.018487274017106304</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007231500464492473</v>
+        <v>0.014515407766472005</v>
       </c>
       <c r="Q2" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R2" t="s">
         <v>47</v>
